--- a/Produkty/658-50060658.xlsx
+++ b/Produkty/658-50060658.xlsx
@@ -445,7 +445,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>1450x60x28-658</v>
+        <v>1450x60x28</v>
       </c>
       <c r="C2" t="str">
         <v>1450</v>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>530x60x28-658</v>
+        <v>530x60x28</v>
       </c>
       <c r="C3" t="str">
         <v>530</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v>200x20x28-658</v>
+        <v>200x20x28</v>
       </c>
       <c r="C4" t="str">
         <v>200</v>
@@ -568,7 +568,7 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v>80x20x28-658</v>
+        <v>80x20x28</v>
       </c>
       <c r="C5" t="str">
         <v>80</v>
@@ -609,7 +609,7 @@
         <v/>
       </c>
       <c r="B6" t="str">
-        <v>550x10x28-658</v>
+        <v>550x10x28</v>
       </c>
       <c r="C6" t="str">
         <v>550</v>
